--- a/data/trans_bre/IP18E_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18E_R1-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,83</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-3,94%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.293331558102929</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.10065050698405</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.314597597516843</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.82847180686513</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.02437673576345726</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05176323762646265</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.02413842678682835</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.03937764131503219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 7,2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; -1,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,55; 2,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-18,37; 4,88</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 7,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,71; -1,29</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 2,19</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-18,95; 5,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.267230696090972</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.572819513848152</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.545612787324975</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.37309081671808</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.02350002789990012</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.09706646738485789</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.07754677299745646</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1895087007913945</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.202820830591218</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-1.247036441591968</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.088245859043389</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.875712366897007</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.07930495585630423</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-0.01289833922028823</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.02186292812355053</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.05033158822304976</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,43</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-4,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 4,37</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 7,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,9; 1,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,73; 4,67</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 4,79</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 8,09</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-5,05; 2,08</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-15,21; 5,07</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.5522984199482939</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.008118185418486</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.324028843445624</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.430152059484027</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.005910472234121567</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.04266669038088022</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01383215925243722</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.04657000376720655</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-11,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-0,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-12,86%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.581768941353293</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8734766200640518</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.896453831131919</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-14.72762099894765</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03768977662673936</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.009110924032719198</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.05054524774087362</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.152060447090001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 4,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,34; 4,94</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 2,79</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-30,33; 2,35</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-7,14; 5,08</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,54; 5,5</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 3,0</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-32,41; 2,39</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.369778446407453</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.360678661669497</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.990112446006028</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.670649331214709</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04790814791035234</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.08088754848572799</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.02076596757515439</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.05074099399184428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,75</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,45</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,27%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.8989287794575307</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1097919939233472</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8775314285110136</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-11.81513661904044</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.009762405556657376</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.00118123806834269</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.009191745563162549</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.128620547304411</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 5,23</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 3,87</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 8,18</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-21,13; 8,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,0; 5,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 4,14</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-0,84; 9,46</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-22,85; 9,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.730676922167253</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.340555539292066</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.864797701506258</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-30.33422986706979</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.07141914362182743</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.045350182728024</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.05055535880686486</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3240891105301613</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.491786107064728</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.940774948745189</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.794548377268685</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.349160714210115</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.05080398819311209</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.05503597146534212</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.02995393254418755</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.02390211261252842</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4355143278444107</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3015438208504362</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.752537360262553</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-7.452454301397815</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.00470306603716571</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.003210628444775347</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04175612248529122</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08272059859530838</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.77586840854993</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.624687333602989</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.9057883808080708</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-21.12668622491836</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04004308757614912</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04863476190526743</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.008422565770238068</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2284641324051379</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.225600972970262</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.869919561865767</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.184574858088469</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.105121660247796</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05817847186906691</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.04142044542902903</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.09461602942063733</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.09927775741844824</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-7,38</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 2,77</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 2,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 2,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,42; -0,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,14; 3,02</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,91; 2,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 2,17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-14,39; -1,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.5266375541216339</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05369189010610009</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.05993594224862342</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-7.383378255313843</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.005660364719058183</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0005671992674663736</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0006368641605210635</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.07889630570803043</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.009945721211036</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.817154248090016</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.108879557455874</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.41608214260037</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02140779879511337</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.01906950021287301</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.02219705650590035</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1438973872452231</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.770843510021321</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.169592177848933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.024141917181573</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.8702447051016832</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03016667033051384</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.02310519564038626</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.02171610236517124</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.009971739753965045</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
